--- a/output/spreadsheet/phrase_catalog_sorted.xlsx
+++ b/output/spreadsheet/phrase_catalog_sorted.xlsx
@@ -1,49 +1,54 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="12000"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="24000" windowHeight="12000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="V2 Review" sheetId="1" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" r:id="rId2"/>
+    <sheet name="V2 Review" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'V2 Review'!$A$1:$M$115</definedName>
+  </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1E7145"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF1E7145"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1F4E78"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF1F4E78"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="6">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -101,7851 +106,7695 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M115"/>
-  <sheetFormatPr defaultRowHeight="20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="1" width="34.0" customWidth="1"/>
-    <col min="2" max="2" width="16.0" customWidth="1"/>
-    <col min="3" max="3" width="24.0" customWidth="1"/>
-    <col min="4" max="4" width="24.0" customWidth="1"/>
-    <col min="5" max="5" width="14.0" customWidth="1"/>
-    <col min="6" max="6" width="48.0" customWidth="1"/>
-    <col min="7" max="7" width="48.0" customWidth="1"/>
-    <col min="8" max="8" width="16.0" customWidth="1"/>
-    <col min="9" max="9" width="18.0" customWidth="1"/>
-    <col min="10" max="10" width="12.0" customWidth="1"/>
-    <col min="11" max="11" width="18.0" customWidth="1"/>
-    <col min="12" max="12" width="20.0" customWidth="1"/>
-    <col min="13" max="13" width="42.0" customWidth="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">phrase_id</t>
+          <t>phrase_id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">catalog</t>
+          <t>catalog</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">family</t>
+          <t>family</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">event</t>
+          <t>event</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">mode</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">english_locked</t>
+          <t>english_locked</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">norwegian_locked</t>
+          <t>norwegian_locked</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">active_status</t>
+          <t>active_status</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">action</t>
+          <t>action</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">record_now</t>
+          <t>record_now</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">approved_for_import</t>
+          <t>approved_for_import</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">approved_for_recording</t>
+          <t>approved_for_recording</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">notes</t>
+          <t>notes</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.above.default.1</t>
+          <t>zone.above.default.1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.above</t>
+          <t>zone.above</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">above_zone</t>
+          <t>above_zone</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ease back slightly.</t>
+          <t>Ease back slightly.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ro ned litt.</t>
+          <t>Ro ned litt.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary HR correction</t>
+          <t>primary HR correction</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.below.default.1</t>
+          <t>zone.below.default.1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.below</t>
+          <t>zone.below</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">below_zone</t>
+          <t>below_zone</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pick it up.</t>
+          <t>Pick it up.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øk litt nå.</t>
+          <t>Øk litt nå.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary HR correction</t>
+          <t>primary HR correction</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.in_zone.default.1</t>
+          <t>zone.in_zone.default.1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.in_zone</t>
+          <t>zone.in_zone</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_zone</t>
+          <t>in_zone</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stay right here.</t>
+          <t>Stay right here.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bli her.</t>
+          <t>Bli her.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">replace_text</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary HR hold cue</t>
+          <t>primary HR hold cue</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.silence.default.1</t>
+          <t>zone.silence.default.1</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.silence</t>
+          <t>zone.silence</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_silence_hold</t>
+          <t>max_silence_hold</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find your pace.</t>
+          <t>Find your pace.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finn rytmen.</t>
+          <t>Finn rytmen.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">low-urgency hold guidance</t>
+          <t>low-urgency hold guidance</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.silence.rest.1</t>
+          <t>zone.silence.rest.1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.silence</t>
+          <t>zone.silence</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_silence_hold</t>
+          <t>max_silence_hold</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Relax your shoulders.</t>
+          <t>Relax your shoulders.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Senk skuldrene.</t>
+          <t>Senk skuldrene.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">low-urgency hold guidance</t>
+          <t>low-urgency hold guidance</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.silence.work.1</t>
+          <t>zone.silence.work.1</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.silence</t>
+          <t>zone.silence</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_silence_hold</t>
+          <t>max_silence_hold</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold the rhythm.</t>
+          <t>Hold the rhythm.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold rytmen.</t>
+          <t>Hold rytmen.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">low-urgency hold guidance</t>
+          <t>low-urgency hold guidance</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.structure.finish.1</t>
+          <t>zone.structure.finish.1</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.structure.finish</t>
+          <t>zone.structure.finish</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">final_effort</t>
+          <t>final_effort</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final push now!</t>
+          <t>Final push now!</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trykk til nå!</t>
+          <t>Trykk til nå!</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary no-HR finish cue</t>
+          <t>primary no-HR finish cue</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.structure.recovery.1</t>
+          <t>zone.structure.recovery.1</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.structure.recovery</t>
+          <t>zone.structure.recovery</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">recovery_start</t>
+          <t>recovery_start</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ease back and recover.</t>
+          <t>Ease back and recover.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ro ned og hent deg inn.</t>
+          <t>Ro ned og hent deg inn.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary no-HR recovery cue</t>
+          <t>primary no-HR recovery cue</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.structure.steady.1</t>
+          <t>zone.structure.steady.1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.structure.steady</t>
+          <t>zone.structure.steady</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">steady_run</t>
+          <t>steady_run</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Settle into the pace.</t>
+          <t>Settle into the pace.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finn rytmen.</t>
+          <t>Finn rytmen.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary no-HR steady cue</t>
+          <t>primary no-HR steady cue</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.structure.steady.2</t>
+          <t>zone.structure.steady.2</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.structure.steady</t>
+          <t>zone.structure.steady</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">steady_run</t>
+          <t>steady_run</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stay with the rhythm.</t>
+          <t>Stay with the rhythm.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bli i rytmen.</t>
+          <t>Bli i rytmen.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no-HR steady cue</t>
+          <t>no-HR steady cue</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.structure.steady.3</t>
+          <t>zone.structure.steady.3</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.structure.steady</t>
+          <t>zone.structure.steady</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">steady_run</t>
+          <t>steady_run</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stay smooth and relaxed.</t>
+          <t>Stay smooth and relaxed.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolig og avslappet.</t>
+          <t>Rolig og avslappet.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no-HR steady cue</t>
+          <t>no-HR steady cue</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.structure.steady.4</t>
+          <t>zone.structure.steady.4</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.structure.steady</t>
+          <t>zone.structure.steady</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">steady_run</t>
+          <t>steady_run</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control the effort here.</t>
+          <t>Control the effort here.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kontroll på innsatsen.</t>
+          <t>Kontroll på innsatsen.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no-HR steady cue</t>
+          <t>no-HR steady cue</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.structure.steady.5</t>
+          <t>zone.structure.steady.5</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.structure.steady</t>
+          <t>zone.structure.steady</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">steady_run</t>
+          <t>steady_run</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keep the pace steady.</t>
+          <t>Keep the pace steady.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold tempoet jevnt.</t>
+          <t>Hold tempoet jevnt.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no-HR steady cue</t>
+          <t>no-HR steady cue</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.structure.steady.6</t>
+          <t>zone.structure.steady.6</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.structure.steady</t>
+          <t>zone.structure.steady</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">steady_run</t>
+          <t>steady_run</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold the phase.</t>
+          <t>Hold the phase.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold det her.</t>
+          <t>Hold det her.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no-HR steady cue</t>
+          <t>no-HR steady cue</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.structure.work.1</t>
+          <t>zone.structure.work.1</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.structure.work</t>
+          <t>zone.structure.work</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval_start</t>
+          <t>interval_start</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pick it up now.</t>
+          <t>Pick it up now.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjør på nå.</t>
+          <t>Kjør på nå.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary no-HR work cue</t>
+          <t>primary no-HR work cue</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.hr_poor_enter.1</t>
+          <t>zone.hr_poor_enter.1</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.hr_poor_enter</t>
+          <t>zone.hr_poor_enter</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hr_signal_lost</t>
+          <t>hr_signal_lost</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heart rate signal is weak.</t>
+          <t>Heart rate signal is weak.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pulssignalet er svakt.</t>
+          <t>Pulssignalet er svakt.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR-dependent context</t>
+          <t>HR-dependent context</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.hr_poor_exit.1</t>
+          <t>zone.hr_poor_exit.1</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.hr_poor_exit</t>
+          <t>zone.hr_poor_exit</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hr_signal_restored</t>
+          <t>hr_signal_restored</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heart rate is back.</t>
+          <t>Heart rate is back.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pulsen er tilbake.</t>
+          <t>Pulsen er tilbake.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR-dependent context</t>
+          <t>HR-dependent context</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.hr_poor_timing.1</t>
+          <t>zone.hr_poor_timing.1</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.hr_poor_timing</t>
+          <t>zone.hr_poor_timing</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no_hr_mode_notice</t>
+          <t>no_hr_mode_notice</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No heart rate signal. I will continue coaching</t>
+          <t>No heart rate signal. I will continue coaching</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingen pulssignal. Jeg fortsetter å coache</t>
+          <t>Ingen pulssignal. Jeg fortsetter å coache</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">primary no-HR mode switch</t>
+          <t>primary no-HR mode switch</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.main_started.1</t>
+          <t>zone.main_started.1</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.main_started</t>
+          <t>zone.main_started</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">main_started</t>
+          <t>main_started</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main set now.</t>
+          <t>Main set now.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nå er du i hoveddelen.</t>
+          <t>Nå er du i hoveddelen.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared main-set context</t>
+          <t>shared main-set context</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.pause.detected.1</t>
+          <t>zone.pause.detected.1</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.pause</t>
+          <t>zone.pause</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pause_detected</t>
+          <t>pause_detected</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paused session</t>
+          <t>Paused session</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pauset økten.</t>
+          <t>Pauset økten.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared pause context</t>
+          <t>shared pause context</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.pause.resumed.1</t>
+          <t>zone.pause.resumed.1</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.pause</t>
+          <t>zone.pause</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pause_resumed</t>
+          <t>pause_resumed</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">You're moving again.</t>
+          <t>You're moving again.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du er i gang igjen.</t>
+          <t>Du er i gang igjen.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared pause context</t>
+          <t>shared pause context</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.cooldown.1</t>
+          <t>zone.phase.cooldown.1</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.cooldown</t>
+          <t>zone.phase.cooldown</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">cooldown</t>
+          <t>cooldown</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooldown now.</t>
+          <t>Cooldown now.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nå roer vi ned.</t>
+          <t>Nå roer vi ned.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared cooldown context</t>
+          <t>shared cooldown context</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.rest.1</t>
+          <t>zone.phase.rest.1</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.rest</t>
+          <t>zone.phase.rest</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">phase_change_rest</t>
+          <t>phase_change_rest</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recovery now.</t>
+          <t>Recovery now.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pause nå.</t>
+          <t>Pause nå.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared recovery context</t>
+          <t>shared recovery context</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.warmup.1</t>
+          <t>zone.phase.warmup.1</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.warmup</t>
+          <t>zone.phase.warmup</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">warmup</t>
+          <t>warmup</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prepare for the session.</t>
+          <t>Prepare for the session.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forbered deg på økten.</t>
+          <t>Forbered deg på økten.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared warmup context</t>
+          <t>shared warmup context</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.work.default.1</t>
+          <t>zone.phase.work.default.1</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.work</t>
+          <t>zone.phase.work</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">phase_change_work</t>
+          <t>phase_change_work</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Work starts now.</t>
+          <t>Work starts now.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nå begynner innsatsen.</t>
+          <t>Nå begynner innsatsen.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared work transition</t>
+          <t>shared work transition</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.work.motivational.1</t>
+          <t>zone.phase.work.motivational.1</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.work</t>
+          <t>zone.phase.work</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">phase_change_work</t>
+          <t>phase_change_work</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time to work.</t>
+          <t>Time to work.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nå jobber vi.</t>
+          <t>Nå jobber vi.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared work transition</t>
+          <t>shared work transition</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.countdown.15</t>
+          <t>zone.countdown.15</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">progress</t>
+          <t>progress</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.countdown</t>
+          <t>zone.countdown</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">countdown_15</t>
+          <t>countdown_15</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15!</t>
+          <t>15!</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15!</t>
+          <t>15!</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared countdown cue</t>
+          <t>shared countdown cue</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.countdown.30</t>
+          <t>zone.countdown.30</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">progress</t>
+          <t>progress</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.countdown</t>
+          <t>zone.countdown</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">countdown_30</t>
+          <t>countdown_30</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30 seconds left.</t>
+          <t>30 seconds left.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30 sekunder.</t>
+          <t>30 sekunder.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared countdown cue</t>
+          <t>shared countdown cue</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.countdown.5</t>
+          <t>zone.countdown.5</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">progress</t>
+          <t>progress</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.countdown</t>
+          <t>zone.countdown</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">countdown_5</t>
+          <t>countdown_5</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5!</t>
+          <t>5!</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5!</t>
+          <t>fem</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared countdown cue</t>
+          <t>shared countdown cue</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.countdown.start</t>
+          <t>zone.countdown.start</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">progress</t>
+          <t>progress</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.countdown</t>
+          <t>zone.countdown</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">countdown_start</t>
+          <t>countdown_start</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Go!</t>
+          <t>Go!</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjør på nå.</t>
+          <t>Kjør på nå.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared countdown start cue</t>
+          <t>shared countdown start cue</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.workout_finished.1</t>
+          <t>zone.workout_finished.1</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">progress</t>
+          <t>progress</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.workout_finished</t>
+          <t>zone.workout_finished</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">workout_finish</t>
+          <t>workout_finish</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Workout finished. Nice work.</t>
+          <t>Workout finished. Nice work.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Økten er ferdig. Bra jobbet.</t>
+          <t>Økten er ferdig. Bra jobbet.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared workout closure</t>
+          <t>shared workout closure</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s1.1</t>
+          <t>easy_run.motivate.s1.1</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s1</t>
+          <t>easy_run.motivate.s1</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run_sustain_stage_1</t>
+          <t>easy_run_sustain_stage_1</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Focus on breath and rhythm.</t>
+          <t>Focus on breath and rhythm.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fokuser på pust og rytme.</t>
+          <t>Fokuser på pust og rytme.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">replace_text</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active easy-run motivation</t>
+          <t>active easy-run motivation</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s1.2</t>
+          <t>easy_run.motivate.s1.2</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s1</t>
+          <t>easy_run.motivate.s1</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run_sustain_stage_1</t>
+          <t>easy_run_sustain_stage_1</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Settle your pace.</t>
+          <t>Settle your pace.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finn ditt tempo.</t>
+          <t>Finn ditt tempo.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">replace_text</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active easy-run motivation</t>
+          <t>active easy-run motivation</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s2.1</t>
+          <t>easy_run.motivate.s2.1</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s2</t>
+          <t>easy_run.motivate.s2</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run_sustain_stage_2</t>
+          <t>easy_run_sustain_stage_2</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Good rhythm.</t>
+          <t>Good rhythm.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bra rytme.</t>
+          <t>Bra rytme.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">replace_text</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active easy-run motivation</t>
+          <t>active easy-run motivation</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s2.2</t>
+          <t>easy_run.motivate.s2.2</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s2</t>
+          <t>easy_run.motivate.s2</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run_sustain_stage_2</t>
+          <t>easy_run_sustain_stage_2</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keep it steady.</t>
+          <t>Keep it steady.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold det jevnt.</t>
+          <t>Hold det jevnt.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">replace_text</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active easy-run motivation</t>
+          <t>active easy-run motivation</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s3.1</t>
+          <t>easy_run.motivate.s3.1</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s3</t>
+          <t>easy_run.motivate.s3</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run_sustain_stage_3</t>
+          <t>easy_run_sustain_stage_3</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nice work!</t>
+          <t>Nice work!</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bra jobba!</t>
+          <t>Bra jobba!</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">replace_text</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active easy-run motivation</t>
+          <t>active easy-run motivation</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s3.2</t>
+          <t>easy_run.motivate.s3.2</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s3</t>
+          <t>easy_run.motivate.s3</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run_sustain_stage_3</t>
+          <t>easy_run_sustain_stage_3</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keep it strong.</t>
+          <t>Keep it strong.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold det sterkt.</t>
+          <t>Hold det sterkt.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">replace_text</t>
+          <t>replace_text</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active easy-run motivation</t>
+          <t>active easy-run motivation</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s4.1</t>
+          <t>easy_run.motivate.s4.1</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s4</t>
+          <t>easy_run.motivate.s4</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run_sustain_stage_4</t>
+          <t>easy_run_sustain_stage_4</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stay smooth.</t>
+          <t>Stay smooth.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold det rolig.</t>
+          <t>Hold det rolig.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active easy-run motivation</t>
+          <t>active easy-run motivation</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s4.2</t>
+          <t>easy_run.motivate.s4.2</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s4</t>
+          <t>easy_run.motivate.s4</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run_sustain_stage_4</t>
+          <t>easy_run_sustain_stage_4</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keep it steady.</t>
+          <t>Keep it steady.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold det jevnt.</t>
+          <t>Hold det jevnt.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active easy-run motivation</t>
+          <t>active easy-run motivation</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s1.1</t>
+          <t>interval.motivate.s1.1</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s1</t>
+          <t>interval.motivate.s1</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval_sustain_stage_1</t>
+          <t>interval_sustain_stage_1</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control your breath.</t>
+          <t>Control your breath.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kontroller pusten.</t>
+          <t>Kontroller pusten.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active interval motivation</t>
+          <t>active interval motivation</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s1.2</t>
+          <t>interval.motivate.s1.2</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s1</t>
+          <t>interval.motivate.s1</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval_sustain_stage_1</t>
+          <t>interval_sustain_stage_1</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Good start.</t>
+          <t>Good start.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">God start.</t>
+          <t>God start.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active interval motivation</t>
+          <t>active interval motivation</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s2.1</t>
+          <t>interval.motivate.s2.1</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s2</t>
+          <t>interval.motivate.s2</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval_sustain_stage_2</t>
+          <t>interval_sustain_stage_2</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nice work.</t>
+          <t>Nice work.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bra jobba.</t>
+          <t>Bra jobba.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">replace_text</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active interval motivation</t>
+          <t>active interval motivation</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s2.2</t>
+          <t>interval.motivate.s2.2</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s2</t>
+          <t>interval.motivate.s2</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval_sustain_stage_2</t>
+          <t>interval_sustain_stage_2</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold the rhythm.</t>
+          <t>Hold the rhythm.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold rytmen.</t>
+          <t>Hold rytmen.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">replace_text</t>
+          <t>replace_text</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active interval motivation</t>
+          <t>active interval motivation</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s3.1</t>
+          <t>interval.motivate.s3.1</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s3</t>
+          <t>interval.motivate.s3</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval_sustain_stage_3</t>
+          <t>interval_sustain_stage_3</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perfect!</t>
+          <t>Perfect!</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herlig!</t>
+          <t>Herlig!</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>replace_text</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active interval motivation</t>
+          <t>active interval motivation</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s3.2</t>
+          <t>interval.motivate.s3.2</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s3</t>
+          <t>interval.motivate.s3</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval_sustain_stage_3</t>
+          <t>interval_sustain_stage_3</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stay with it!</t>
+          <t>Stay with it!</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stå i det!</t>
+          <t>Stå i det!</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active interval motivation</t>
+          <t>active interval motivation</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s4.1</t>
+          <t>interval.motivate.s4.1</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s4</t>
+          <t>interval.motivate.s4</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval_sustain_stage_4</t>
+          <t>interval_sustain_stage_4</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finish strong!</t>
+          <t>Finish strong!</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjør på nå!</t>
+          <t>Kjør på nå!</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">replace_text</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active interval motivation</t>
+          <t>active interval motivation</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s4.2</t>
+          <t>interval.motivate.s4.2</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s4</t>
+          <t>interval.motivate.s4</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval_sustain_stage_4</t>
+          <t>interval_sustain_stage_4</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">All the way in.</t>
+          <t>All the way in.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helt inn!</t>
+          <t>Helt inn!</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">replace_text</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active interval motivation</t>
+          <t>active interval motivation</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.no_sensors.1</t>
+          <t>zone.no_sensors.1</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.no_sensors</t>
+          <t>zone.no_sensors</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no_sensors</t>
+          <t>no_sensors</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIAGNOSTIC</t>
+          <t>DIAGNOSTIC</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coaching by breath.</t>
+          <t>Coaching by breath.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coacher med pust.</t>
+          <t>Coacher med pust.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active_secondary</t>
+          <t>active_secondary</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">secondary no-sensors diagnostic</t>
+          <t>secondary no-sensors diagnostic</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.watch_disconnected.1</t>
+          <t>zone.watch_disconnected.1</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.watch</t>
+          <t>zone.watch</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">watch_lost</t>
+          <t>watch_lost</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIAGNOSTIC</t>
+          <t>DIAGNOSTIC</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Watch disconnected</t>
+          <t>Watch disconnected</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pulsklokken ble frakoblet.</t>
+          <t>Pulsklokken ble frakoblet.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active_secondary</t>
+          <t>active_secondary</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">secondary watch-loss diagnostic</t>
+          <t>secondary watch-loss diagnostic</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.watch_restored.1</t>
+          <t>zone.watch_restored.1</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.watch</t>
+          <t>zone.watch</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">watch_restored</t>
+          <t>watch_restored</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIAGNOSTIC</t>
+          <t>DIAGNOSTIC</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Watch connected and heart rate is back.</t>
+          <t>Watch connected and heart rate is back.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klokken er tilkoblet, og pulsen er tilbake.</t>
+          <t>Klokken er tilkoblet, og pulsen er tilbake.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">active_secondary</t>
+          <t>active_secondary</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t>keep</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">secondary watch-restore diagnostic</t>
+          <t>secondary watch-restore diagnostic</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.above.minimal.1</t>
+          <t>zone.above.minimal.1</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.above</t>
+          <t>zone.above</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">above_zone</t>
+          <t>above_zone</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ease off 10-15 seconds.</t>
+          <t>Ease off 10-15 seconds.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Litt ned 10-15 sekunder.</t>
+          <t>Litt ned 10-15 sekunder.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr"/>
+      <c r="L52" s="4" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy HR correction variant</t>
+          <t>legacy HR correction variant</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.above_ease.default.1</t>
+          <t>zone.above_ease.default.1</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.above_ease</t>
+          <t>zone.above_ease</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">above_zone_ease</t>
+          <t>above_zone_ease</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Still high. Ease down 20 seconds.</t>
+          <t>Still high. Ease down 20 seconds.</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fortsatt høy. Ro ned 20 sekunder.</t>
+          <t>Fortsatt høy. Ro ned 20 sekunder.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K53" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr"/>
+      <c r="L53" s="4" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy sustained HR correction variant</t>
+          <t>legacy sustained HR correction variant</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.above_ease.minimal.1</t>
+          <t>zone.above_ease.minimal.1</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.above_ease</t>
+          <t>zone.above_ease</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">above_zone_ease</t>
+          <t>above_zone_ease</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR still climbing. Ease down.</t>
+          <t>HR still climbing. Ease down.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pulsen stiger. Rolig ned.</t>
+          <t>Pulsen stiger. Rolig ned.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K54" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr"/>
+      <c r="L54" s="4" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy sustained HR correction variant</t>
+          <t>legacy sustained HR correction variant</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.below.minimal.1</t>
+          <t>zone.below.minimal.1</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.below</t>
+          <t>zone.below</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">below_zone</t>
+          <t>below_zone</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Build slightly now.</t>
+          <t>Build slightly now.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygg litt opp nå.</t>
+          <t>Bygg litt opp nå.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K55" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr"/>
+      <c r="L55" s="4" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy HR correction variant</t>
+          <t>legacy HR correction variant</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.below_push.default.1</t>
+          <t>zone.below_push.default.1</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.below_push</t>
+          <t>zone.below_push</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">below_zone_push</t>
+          <t>below_zone_push</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">You're moving. Pick it up slightly.</t>
+          <t>You're moving. Pick it up slightly.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du er i gang. Øk litt.</t>
+          <t>Du er i gang. Øk litt.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr"/>
+      <c r="L56" s="4" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy sustained HR push variant</t>
+          <t>legacy sustained HR push variant</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.below_push.minimal.1</t>
+          <t>zone.below_push.minimal.1</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.below_push</t>
+          <t>zone.below_push</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">below_zone_push</t>
+          <t>below_zone_push</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">You're moving. Add a little.</t>
+          <t>You're moving. Add a little.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du er i gang. Litt opp.</t>
+          <t>Du er i gang. Litt opp.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K57" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr"/>
+      <c r="L57" s="4" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy sustained HR push variant</t>
+          <t>legacy sustained HR push variant</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.breath.easy_run.1</t>
+          <t>zone.breath.easy_run.1</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.breath.easy_run</t>
+          <t>zone.breath.easy_run</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_silence_breath_guide</t>
+          <t>max_silence_breath_guide</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Match your breathing to your pace.</t>
+          <t>Match your breathing to your pace.</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tilpass pusten til tempoet.</t>
+          <t>Tilpass pusten til tempoet.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr"/>
+      <c r="L58" s="4" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy breath guidance</t>
+          <t>legacy breath guidance</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.breath.easy_run.2</t>
+          <t>zone.breath.easy_run.2</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.breath.easy_run</t>
+          <t>zone.breath.easy_run</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_silence_breath_guide</t>
+          <t>max_silence_breath_guide</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smooth breaths. You're doing well.</t>
+          <t>Smooth breaths. You're doing well.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jevn pust. Du gjør det bra.</t>
+          <t>Jevn pust. Du gjør det bra.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr"/>
+      <c r="L59" s="4" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy breath guidance</t>
+          <t>legacy breath guidance</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.breath.recovery.1</t>
+          <t>zone.breath.recovery.1</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.breath.recovery</t>
+          <t>zone.breath.recovery</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_silence_breath_guide</t>
+          <t>max_silence_breath_guide</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slow your breathing down.</t>
+          <t>Slow your breathing down.</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Senk pustetakten.</t>
+          <t>Senk pustetakten.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr"/>
+      <c r="L60" s="4" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy breath guidance</t>
+          <t>legacy breath guidance</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.breath.work.1</t>
+          <t>zone.breath.work.1</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.breath.work</t>
+          <t>zone.breath.work</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_silence_breath_guide</t>
+          <t>max_silence_breath_guide</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breathe through the effort.</t>
+          <t>Breathe through the effort.</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herlig</t>
+          <t>Herlig</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K61" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr"/>
+      <c r="L61" s="4" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy breath guidance</t>
+          <t>legacy breath guidance</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.feel.easy_run.1</t>
+          <t>zone.feel.easy_run.1</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.feel.easy_run</t>
+          <t>zone.feel.easy_run</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_silence_go_by_feel</t>
+          <t>max_silence_go_by_feel</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steady effort. Stay comfortable.</t>
+          <t>Steady effort. Stay comfortable.</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jevn innsats. Hold det behagelig.</t>
+          <t>Jevn innsats. Hold det behagelig.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr"/>
+      <c r="L62" s="4" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy no-HR feel guidance</t>
+          <t>legacy no-HR feel guidance</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.feel.easy_run.2</t>
+          <t>zone.feel.easy_run.2</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.feel.easy_run</t>
+          <t>zone.feel.easy_run</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_silence_go_by_feel</t>
+          <t>max_silence_go_by_feel</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find your rhythm and hold it.</t>
+          <t>Find your rhythm and hold it.</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finn rytmen din og hold den.</t>
+          <t>Finn rytmen din og hold den.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr"/>
+      <c r="L63" s="4" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy no-HR feel guidance</t>
+          <t>legacy no-HR feel guidance</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.feel.easy_run.3</t>
+          <t>zone.feel.easy_run.3</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.feel.easy_run</t>
+          <t>zone.feel.easy_run</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_silence_go_by_feel</t>
+          <t>max_silence_go_by_feel</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Easy and controlled. You set the pace.</t>
+          <t>Easy and controlled. You set the pace.</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolig og kontrollert. Du bestemmer tempoet.</t>
+          <t>Rolig og kontrollert. Du bestemmer tempoet.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr"/>
+      <c r="L64" s="4" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy no-HR feel guidance</t>
+          <t>legacy no-HR feel guidance</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.feel.recovery.1</t>
+          <t>zone.feel.recovery.1</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.feel.recovery</t>
+          <t>zone.feel.recovery</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_silence_go_by_feel</t>
+          <t>max_silence_go_by_feel</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ease off. Let your body recover.</t>
+          <t>Ease off. Let your body recover.</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slipp av. La kroppen hente seg inn.</t>
+          <t>Slipp av. La kroppen hente seg inn.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="inlineStr"/>
+      <c r="L65" s="4" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy no-HR feel guidance</t>
+          <t>legacy no-HR feel guidance</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.feel.recovery.2</t>
+          <t>zone.feel.recovery.2</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.feel.recovery</t>
+          <t>zone.feel.recovery</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_silence_go_by_feel</t>
+          <t>max_silence_go_by_feel</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Relax and breathe. Recovery counts.</t>
+          <t>Relax and breathe. Recovery counts.</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slapp av og pust. Hvile teller.</t>
+          <t>Slapp av og pust. Hvile teller.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr"/>
+      <c r="L66" s="4" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy no-HR feel guidance</t>
+          <t>legacy no-HR feel guidance</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.feel.work.1</t>
+          <t>zone.feel.work.1</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.feel.work</t>
+          <t>zone.feel.work</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_silence_go_by_feel</t>
+          <t>max_silence_go_by_feel</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Push hard but controlled.</t>
+          <t>Push hard but controlled.</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold en jevn rytme</t>
+          <t>Hold en jevn rytme</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr"/>
+      <c r="L67" s="4" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy no-HR feel guidance</t>
+          <t>legacy no-HR feel guidance</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.feel.work.2</t>
+          <t>zone.feel.work.2</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.feel.work</t>
+          <t>zone.feel.work</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_silence_go_by_feel</t>
+          <t>max_silence_go_by_feel</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strong effort now. Stay focused.</t>
+          <t>Strong effort now. Stay focused.</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sterk innsats nå. Hold fokus.</t>
+          <t>Sterk innsats nå. Hold fokus.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K68" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr"/>
+      <c r="L68" s="4" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy no-HR feel guidance</t>
+          <t>legacy no-HR feel guidance</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.in_zone.minimal.1</t>
+          <t>zone.in_zone.minimal.1</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.in_zone</t>
+          <t>zone.in_zone</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_zone</t>
+          <t>in_zone</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Good. Stay here.</t>
+          <t>Good. Stay here.</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bli her.</t>
+          <t>Bli her.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr"/>
+      <c r="L69" s="4" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy HR hold variant</t>
+          <t>legacy HR hold variant</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation.1</t>
+          <t>motivation.1</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy_fallback</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nice work!</t>
+          <t>Nice work!</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold det sterkt.</t>
+          <t>Hold det sterkt.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K70" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr"/>
+      <c r="L70" s="4" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy flat motivation pool</t>
+          <t>legacy flat motivation pool</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation.10</t>
+          <t>motivation.10</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy_fallback</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finish what you started.</t>
+          <t>Finish what you started.</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fullfør det du begynte på.</t>
+          <t>Fullfør det du begynte på.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K71" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr"/>
+      <c r="L71" s="4" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy flat motivation pool</t>
+          <t>legacy flat motivation pool</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation.2</t>
+          <t>motivation.2</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy_fallback</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keep it up.</t>
+          <t>Keep it up.</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bra jobba!</t>
+          <t>Bra jobba!</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K72" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L72" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr"/>
+      <c r="L72" s="4" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy flat motivation pool</t>
+          <t>legacy flat motivation pool</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation.3</t>
+          <t>motivation.3</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy_fallback</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">That's the effort I want to see.</t>
+          <t>That's the effort I want to see.</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Det skal kjennes litt. Det er prisen for endring..</t>
+          <t>Det skal kjennes litt. Det er prisen for endring..</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K73" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr"/>
+      <c r="L73" s="4" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy flat motivation pool</t>
+          <t>legacy flat motivation pool</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation.4</t>
+          <t>motivation.4</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy_fallback</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">One step at a time. You got this.</t>
+          <t>One step at a time. You got this.</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ett steg om gangen. Du klarer det.</t>
+          <t>Ett steg om gangen. Du klarer det.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K74" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr"/>
+      <c r="L74" s="4" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy flat motivation pool</t>
+          <t>legacy flat motivation pool</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation.5</t>
+          <t>motivation.5</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy_fallback</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discipline beats motivation. Keep going.</t>
+          <t>Discipline beats motivation. Keep going.</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Disiplin slår motivasjon. Fortsett.</t>
+          <t>Disiplin slår motivasjon. Fortsett.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K75" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr"/>
+      <c r="L75" s="4" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy flat motivation pool</t>
+          <t>legacy flat motivation pool</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation.6</t>
+          <t>motivation.6</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy_fallback</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is where it counts.</t>
+          <t>This is where it counts.</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Det er nå det gjelder.</t>
+          <t>Det er nå det gjelder.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr"/>
+      <c r="L76" s="4" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy flat motivation pool</t>
+          <t>legacy flat motivation pool</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation.7</t>
+          <t>motivation.7</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy_fallback</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">You showed up. thats the hard part.</t>
+          <t>You showed up. thats the hard part.</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du møtte opp. Det er det vanskelige.</t>
+          <t>Du møtte opp. Det er det vanskelige.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr"/>
+      <c r="L77" s="4" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy flat motivation pool</t>
+          <t>legacy flat motivation pool</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation.8</t>
+          <t>motivation.8</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy_fallback</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trust the process.</t>
+          <t>Trust the process.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stol på prosessen.</t>
+          <t>Stol på prosessen.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K78" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr"/>
+      <c r="L78" s="4" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy flat motivation pool</t>
+          <t>legacy flat motivation pool</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation.9</t>
+          <t>motivation.9</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy_fallback</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Every rep matters.</t>
+          <t>Every rep matters.</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvert steg teller.</t>
+          <t>Hvert steg teller.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility</t>
+          <t>compatibility</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">compatibility_only</t>
+          <t>compatibility_only</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="K79" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="inlineStr"/>
+      <c r="L79" s="4" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">legacy flat motivation pool</t>
+          <t>legacy flat motivation pool</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.hr_poor_enter.2</t>
+          <t>zone.hr_poor_enter.2</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.hr_poor_enter</t>
+          <t>zone.hr_poor_enter</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hr_signal_lost</t>
+          <t>hr_signal_lost</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heart rate signal dropped.</t>
+          <t>Heart rate signal dropped.</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pulssignalet falt ut.</t>
+          <t>Pulssignalet falt ut.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K80" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr"/>
+      <c r="L80" s="4" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future HR-loss variant</t>
+          <t>future HR-loss variant</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.hr_poor_exit.2</t>
+          <t>zone.hr_poor_exit.2</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.hr_poor_exit</t>
+          <t>zone.hr_poor_exit</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hr_signal_restored</t>
+          <t>hr_signal_restored</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heart rate is stable again.</t>
+          <t>Heart rate is stable again.</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pulsen er stabil igjen.</t>
+          <t>Pulsen er stabil igjen.</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K81" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K81" s="4" t="inlineStr"/>
+      <c r="L81" s="4" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future HR-restore variant</t>
+          <t>future HR-restore variant</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.hr_poor_timing.2</t>
+          <t>zone.hr_poor_timing.2</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.hr_poor_timing</t>
+          <t>zone.hr_poor_timing</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">no_hr_mode_notice</t>
+          <t>no_hr_mode_notice</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_HR</t>
+          <t>NO_HR</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heart rate unavailable. Coaching, keep moving.</t>
+          <t>Heart rate unavailable. Coaching, keep moving.</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pulssignal mangler. Jeg fortsetter å coache</t>
+          <t>Pulssignal mangler. Jeg fortsetter å coache</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K82" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K82" s="4" t="inlineStr"/>
+      <c r="L82" s="4" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future no-HR mode-switch variant</t>
+          <t>future no-HR mode-switch variant</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.main_started.2</t>
+          <t>zone.main_started.2</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.main_started</t>
+          <t>zone.main_started</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">main_started</t>
+          <t>main_started</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The workout begins now.</t>
+          <t>The workout begins now.</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nå begynner økten.</t>
+          <t>Nå begynner økten.</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K83" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K83" s="4" t="inlineStr"/>
+      <c r="L83" s="4" t="inlineStr"/>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future shared main-set variant</t>
+          <t>future shared main-set variant</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.main_started.3</t>
+          <t>zone.main_started.3</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.main_started</t>
+          <t>zone.main_started</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">main_started</t>
+          <t>main_started</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main work starts now.</t>
+          <t>Main work starts now.</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hoveddelen starter nå.</t>
+          <t>Hoveddelen starter nå.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K84" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K84" s="4" t="inlineStr"/>
+      <c r="L84" s="4" t="inlineStr"/>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future shared main-set variant</t>
+          <t>future shared main-set variant</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.pause.detected.2</t>
+          <t>zone.pause.detected.2</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.pause</t>
+          <t>zone.pause</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pause_detected</t>
+          <t>pause_detected</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stopped.</t>
+          <t>Stopped.</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stoppet.</t>
+          <t>Stoppet.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K85" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K85" s="4" t="inlineStr"/>
+      <c r="L85" s="4" t="inlineStr"/>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future pause-detected variant</t>
+          <t>future pause-detected variant</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.pause.resumed.2</t>
+          <t>zone.pause.resumed.2</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.pause</t>
+          <t>zone.pause</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pause_resumed</t>
+          <t>pause_resumed</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Workout continues.</t>
+          <t>Workout continues.</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Økten fortsetter.</t>
+          <t>Økten fortsetter.</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K86" s="4" t="inlineStr"/>
+      <c r="L86" s="4" t="inlineStr"/>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future pause-resumed variant</t>
+          <t>future pause-resumed variant</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.cooldown.2</t>
+          <t>zone.phase.cooldown.2</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.cooldown</t>
+          <t>zone.phase.cooldown</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">cooldown</t>
+          <t>cooldown</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bring it down.</t>
+          <t>Bring it down.</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ro ned.</t>
+          <t>Ro ned.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K87" s="4" t="inlineStr"/>
+      <c r="L87" s="4" t="inlineStr"/>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future shared cooldown variant</t>
+          <t>future shared cooldown variant</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.cooldown.3</t>
+          <t>zone.phase.cooldown.3</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.cooldown</t>
+          <t>zone.phase.cooldown</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">cooldown</t>
+          <t>cooldown</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slow it down.</t>
+          <t>Slow it down.</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vi roer ned nå.</t>
+          <t>Vi roer ned nå.</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K88" s="4" t="inlineStr"/>
+      <c r="L88" s="4" t="inlineStr"/>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future shared cooldown variant</t>
+          <t>future shared cooldown variant</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.rest.2</t>
+          <t>zone.phase.rest.2</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.rest</t>
+          <t>zone.phase.rest</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">phase_change_rest</t>
+          <t>phase_change_rest</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Calm your breath now.</t>
+          <t>Calm your breath now.</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ro ned pusten nå.</t>
+          <t>Ro ned pusten nå.</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K89" s="4" t="inlineStr"/>
+      <c r="L89" s="4" t="inlineStr"/>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future shared recovery variant</t>
+          <t>future shared recovery variant</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.rest.3</t>
+          <t>zone.phase.rest.3</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.rest</t>
+          <t>zone.phase.rest</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">phase_change_rest</t>
+          <t>phase_change_rest</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catch your breath.</t>
+          <t>Catch your breath.</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hent deg inn nå.</t>
+          <t>Hent deg inn nå.</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K90" s="4" t="inlineStr"/>
+      <c r="L90" s="4" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future shared recovery variant</t>
+          <t>future shared recovery variant</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.warmup.2</t>
+          <t>zone.phase.warmup.2</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.warmup</t>
+          <t>zone.phase.warmup</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">warmup</t>
+          <t>warmup</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Easy start.</t>
+          <t>Easy start.</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolig start.</t>
+          <t>Rolig start.</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K91" s="4" t="inlineStr"/>
+      <c r="L91" s="4" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future shared warmup variant</t>
+          <t>future shared warmup variant</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.warmup.3</t>
+          <t>zone.phase.warmup.3</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.phase.warmup</t>
+          <t>zone.phase.warmup</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">warmup</t>
+          <t>warmup</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start nice and easy.</t>
+          <t>Start nice and easy.</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start rolig.</t>
+          <t>Start rolig.</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K92" s="4" t="inlineStr"/>
+      <c r="L92" s="4" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future shared warmup variant</t>
+          <t>future shared warmup variant</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.above.default.2</t>
+          <t>zone.above.default.2</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.above</t>
+          <t>zone.above</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">above_zone</t>
+          <t>above_zone</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bring it down.</t>
+          <t>Bring it down.</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Senk tempoet litt.</t>
+          <t>Senk tempoet litt.</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K93" s="4" t="inlineStr"/>
+      <c r="L93" s="4" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future HR correction variant</t>
+          <t>future HR correction variant</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.above.default.3</t>
+          <t>zone.above.default.3</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.above</t>
+          <t>zone.above</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">above_zone</t>
+          <t>above_zone</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ease the effort.</t>
+          <t>Ease the effort.</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ro ned innsatsen.</t>
+          <t>Ro ned innsatsen.</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K94" s="4" t="inlineStr"/>
+      <c r="L94" s="4" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future HR correction variant</t>
+          <t>future HR correction variant</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.above.default.4</t>
+          <t>zone.above.default.4</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.above</t>
+          <t>zone.above</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">above_zone</t>
+          <t>above_zone</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Settle it down.</t>
+          <t>Settle it down.</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La det roe seg.</t>
+          <t>La det roe seg.</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K95" s="4" t="inlineStr"/>
+      <c r="L95" s="4" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future HR correction variant</t>
+          <t>future HR correction variant</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.above.default.5</t>
+          <t>zone.above.default.5</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.above</t>
+          <t>zone.above</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">above_zone</t>
+          <t>above_zone</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Relax the pace.</t>
+          <t>Relax the pace.</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slipp litt opp.</t>
+          <t>Slipp litt opp.</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K96" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr"/>
+      <c r="L96" s="4" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future HR correction variant</t>
+          <t>future HR correction variant</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.below.default.2</t>
+          <t>zone.below.default.2</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.below</t>
+          <t>zone.below</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">below_zone</t>
+          <t>below_zone</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bring the effort up.</t>
+          <t>Bring the effort up.</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Litt mer innsats.</t>
+          <t>Litt mer innsats.</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K97" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K97" s="4" t="inlineStr"/>
+      <c r="L97" s="4" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future HR correction variant</t>
+          <t>future HR correction variant</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.below.default.3</t>
+          <t>zone.below.default.3</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.below</t>
+          <t>zone.below</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">below_zone</t>
+          <t>below_zone</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lift the pace.</t>
+          <t>Lift the pace.</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øk tempoet litt.</t>
+          <t>Øk tempoet litt.</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K98" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K98" s="4" t="inlineStr"/>
+      <c r="L98" s="4" t="inlineStr"/>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future HR correction variant</t>
+          <t>future HR correction variant</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.below.default.4</t>
+          <t>zone.below.default.4</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.below</t>
+          <t>zone.below</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">below_zone</t>
+          <t>below_zone</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drive the pace.</t>
+          <t>Drive the pace.</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trykk til litt.</t>
+          <t>Trykk til litt.</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K99" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K99" s="4" t="inlineStr"/>
+      <c r="L99" s="4" t="inlineStr"/>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future HR correction variant</t>
+          <t>future HR correction variant</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.below.default.5</t>
+          <t>zone.below.default.5</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.below</t>
+          <t>zone.below</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">below_zone</t>
+          <t>below_zone</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Build the effort.</t>
+          <t>Build the effort.</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygg opp innsatsen.</t>
+          <t>Bygg opp innsatsen.</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K100" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K100" s="4" t="inlineStr"/>
+      <c r="L100" s="4" t="inlineStr"/>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future HR correction variant</t>
+          <t>future HR correction variant</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.in_zone.default.2</t>
+          <t>zone.in_zone.default.2</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.in_zone</t>
+          <t>zone.in_zone</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_zone</t>
+          <t>in_zone</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold this pace.</t>
+          <t>Hold this pace.</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold dette tempoet.</t>
+          <t>Hold dette tempoet.</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K101" s="4" t="inlineStr"/>
+      <c r="L101" s="4" t="inlineStr"/>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future HR hold variant</t>
+          <t>future HR hold variant</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.in_zone.default.3</t>
+          <t>zone.in_zone.default.3</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.in_zone</t>
+          <t>zone.in_zone</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_zone</t>
+          <t>in_zone</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold the rhythm.</t>
+          <t>Hold the rhythm.</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold rytmen.</t>
+          <t>Hold rytmen.</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K102" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="inlineStr"/>
+      <c r="L102" s="4" t="inlineStr"/>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future HR hold variant</t>
+          <t>future HR hold variant</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.in_zone.default.4</t>
+          <t>zone.in_zone.default.4</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.in_zone</t>
+          <t>zone.in_zone</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_zone</t>
+          <t>in_zone</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stay steady.</t>
+          <t>Stay steady.</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold det jevnt.</t>
+          <t>Hold det jevnt.</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K103" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K103" s="4" t="inlineStr"/>
+      <c r="L103" s="4" t="inlineStr"/>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future HR hold variant</t>
+          <t>future HR hold variant</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.in_zone.default.5</t>
+          <t>zone.in_zone.default.5</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instruction</t>
+          <t>instruction</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.in_zone</t>
+          <t>zone.in_zone</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">in_zone</t>
+          <t>in_zone</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Right there.</t>
+          <t>Right there.</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Der ja!</t>
+          <t>Der ja!</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K104" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K104" s="4" t="inlineStr"/>
+      <c r="L104" s="4" t="inlineStr"/>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future HR hold variant</t>
+          <t>future HR hold variant</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s1.3</t>
+          <t>easy_run.motivate.s1.3</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s1</t>
+          <t>easy_run.motivate.s1</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run_sustain_stage_1</t>
+          <t>easy_run_sustain_stage_1</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nice and easy.</t>
+          <t>Nice and easy.</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start rolig!</t>
+          <t>Start rolig!</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K105" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L105" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K105" s="4" t="inlineStr"/>
+      <c r="L105" s="4" t="inlineStr"/>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future easy-run motivation variant</t>
+          <t>future easy-run motivation variant</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s2.3</t>
+          <t>easy_run.motivate.s2.3</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s2</t>
+          <t>easy_run.motivate.s2</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run_sustain_stage_2</t>
+          <t>easy_run_sustain_stage_2</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stay relaxed.</t>
+          <t>Stay relaxed.</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold deg avslappet.</t>
+          <t>Hold deg avslappet.</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K106" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L106" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K106" s="4" t="inlineStr"/>
+      <c r="L106" s="4" t="inlineStr"/>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future easy-run motivation variant</t>
+          <t>future easy-run motivation variant</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s3.3</t>
+          <t>easy_run.motivate.s3.3</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s3</t>
+          <t>easy_run.motivate.s3</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run_sustain_stage_3</t>
+          <t>easy_run_sustain_stage_3</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keep your flow.</t>
+          <t>Keep your flow.</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold flyten.</t>
+          <t>Hold flyten.</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K107" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L107" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K107" s="4" t="inlineStr"/>
+      <c r="L107" s="4" t="inlineStr"/>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future easy-run motivation variant</t>
+          <t>future easy-run motivation variant</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s4.3</t>
+          <t>easy_run.motivate.s4.3</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run.motivate.s4</t>
+          <t>easy_run.motivate.s4</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">easy_run_sustain_stage_4</t>
+          <t>easy_run_sustain_stage_4</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Right to the end.</t>
+          <t>Right to the end.</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helt til slutt.</t>
+          <t>Helt til slutt.</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K108" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K108" s="4" t="inlineStr"/>
+      <c r="L108" s="4" t="inlineStr"/>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future easy-run motivation variant</t>
+          <t>future easy-run motivation variant</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s1.3</t>
+          <t>interval.motivate.s1.3</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s1</t>
+          <t>interval.motivate.s1</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval_sustain_stage_1</t>
+          <t>interval_sustain_stage_1</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steady pace.</t>
+          <t>Steady pace.</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finn rytmen.</t>
+          <t>Finn rytmen.</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K109" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K109" s="4" t="inlineStr"/>
+      <c r="L109" s="4" t="inlineStr"/>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future interval motivation variant</t>
+          <t>future interval motivation variant</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s2.3</t>
+          <t>interval.motivate.s2.3</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s2</t>
+          <t>interval.motivate.s2</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval_sustain_stage_2</t>
+          <t>interval_sustain_stage_2</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keep it steady.</t>
+          <t>Keep it steady.</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold det jevnt.</t>
+          <t>Hold det jevnt.</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K110" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K110" s="4" t="inlineStr"/>
+      <c r="L110" s="4" t="inlineStr"/>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future interval motivation variant</t>
+          <t>future interval motivation variant</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s3.3</t>
+          <t>interval.motivate.s3.3</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s3</t>
+          <t>interval.motivate.s3</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval_sustain_stage_3</t>
+          <t>interval_sustain_stage_3</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stay strong!</t>
+          <t>Stay strong!</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hold deg sterk!</t>
+          <t>Hold deg sterk!</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K111" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K111" s="4" t="inlineStr"/>
+      <c r="L111" s="4" t="inlineStr"/>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future interval motivation variant</t>
+          <t>future interval motivation variant</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s4.3</t>
+          <t>interval.motivate.s4.3</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">motivation</t>
+          <t>motivation</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval.motivate.s4</t>
+          <t>interval.motivate.s4</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">interval_sustain_stage_4</t>
+          <t>interval_sustain_stage_4</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">HR</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perfect!</t>
+          <t>Perfect!</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herlig!</t>
+          <t>Herlig!</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K112" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K112" s="4" t="inlineStr"/>
+      <c r="L112" s="4" t="inlineStr"/>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future interval motivation variant</t>
+          <t>future interval motivation variant</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.countdown.start.2</t>
+          <t>zone.countdown.start.2</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">progress</t>
+          <t>progress</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.countdown</t>
+          <t>zone.countdown</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">countdown_start</t>
+          <t>countdown_start</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start!</t>
+          <t>Start!</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start!</t>
+          <t>Start!</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K113" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L113" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K113" s="4" t="inlineStr"/>
+      <c r="L113" s="4" t="inlineStr"/>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future countdown-start variant</t>
+          <t>future countdown-start variant</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.workout_finished.2</t>
+          <t>zone.workout_finished.2</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">progress</t>
+          <t>progress</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.workout_finished</t>
+          <t>zone.workout_finished</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">workout_finish</t>
+          <t>workout_finish</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">That’s the workout done.</t>
+          <t>That’s the workout done.</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Der er økta ferdig.</t>
+          <t>Der er økta ferdig.</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K114" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L114" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K114" s="4" t="inlineStr"/>
+      <c r="L114" s="4" t="inlineStr"/>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future workout-finish variant</t>
+          <t>future workout-finish variant</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.workout_finished.3</t>
+          <t>zone.workout_finished.3</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">progress</t>
+          <t>progress</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zone.workout_finished</t>
+          <t>zone.workout_finished</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">workout_finish</t>
+          <t>workout_finish</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Session complete. Nice work.</t>
+          <t>Session complete. Nice work.</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Økta er fullført. Bra jobbet.</t>
+          <t>Økta er fullført. Bra jobbet.</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t>future</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future_add</t>
+          <t>future_add</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K115" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K115" s="4" t="inlineStr"/>
+      <c r="L115" s="4" t="inlineStr"/>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">future workout-finish variant</t>
+          <t>future workout-finish variant</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M115"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">V2 Phrase Review Summary</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+          <t>V2 Phrase Review Summary</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Total rows</t>
+          <t>Total rows</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114</t>
+          <t>114</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Active rows</t>
+          <t>Active rows</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Record-now rows</t>
+          <t>Record-now rows</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compatibility rows</t>
+          <t>Compatibility rows</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Future rows</t>
+          <t>Future rows</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tip</t>
+          <t>Tip</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Set approved_for_import / approved_for_recording to yes after review.</t>
+          <t>Set approved_for_import / approved_for_recording to yes after review.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/spreadsheet/phrase_catalog_sorted.xlsx
+++ b/output/spreadsheet/phrase_catalog_sorted.xlsx
@@ -2253,12 +2253,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>15!</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>15!</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Go!</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Kjør på nå.</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3884,8 +3884,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>legacy HR correction variant</t>
@@ -3943,8 +3941,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>legacy sustained HR correction variant</t>
@@ -4002,8 +3998,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>legacy sustained HR correction variant</t>
@@ -4061,8 +4055,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>legacy HR correction variant</t>
@@ -4120,8 +4112,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
           <t>legacy sustained HR push variant</t>
@@ -4179,8 +4169,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>legacy sustained HR push variant</t>
@@ -4238,8 +4226,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
           <t>legacy breath guidance</t>
@@ -4297,8 +4283,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
           <t>legacy breath guidance</t>
@@ -4356,8 +4340,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>legacy breath guidance</t>
@@ -4415,8 +4397,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>legacy breath guidance</t>
@@ -4474,8 +4454,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>legacy no-HR feel guidance</t>
@@ -4533,8 +4511,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
           <t>legacy no-HR feel guidance</t>
@@ -4592,8 +4568,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
           <t>legacy no-HR feel guidance</t>
@@ -4651,8 +4625,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
           <t>legacy no-HR feel guidance</t>
@@ -4710,8 +4682,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
           <t>legacy no-HR feel guidance</t>
@@ -4769,8 +4739,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>legacy no-HR feel guidance</t>
@@ -4828,8 +4796,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
           <t>legacy no-HR feel guidance</t>
@@ -4887,8 +4853,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
           <t>legacy HR hold variant</t>
@@ -4946,8 +4910,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
           <t>legacy flat motivation pool</t>
@@ -5005,8 +4967,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>legacy flat motivation pool</t>
@@ -5064,8 +5024,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>legacy flat motivation pool</t>
@@ -5123,8 +5081,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
           <t>legacy flat motivation pool</t>
@@ -5182,8 +5138,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
           <t>legacy flat motivation pool</t>
@@ -5241,8 +5195,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
           <t>legacy flat motivation pool</t>
@@ -5300,8 +5252,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
           <t>legacy flat motivation pool</t>
@@ -5359,8 +5309,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
           <t>legacy flat motivation pool</t>
@@ -5418,8 +5366,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
           <t>legacy flat motivation pool</t>
@@ -5477,8 +5423,6 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
           <t>legacy flat motivation pool</t>
@@ -5536,8 +5480,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
           <t>future HR-loss variant</t>
@@ -5595,8 +5537,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
           <t>future HR-restore variant</t>
@@ -5654,8 +5594,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
           <t>future no-HR mode-switch variant</t>
@@ -5713,8 +5651,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
           <t>future shared main-set variant</t>
@@ -5772,8 +5708,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
           <t>future shared main-set variant</t>
@@ -5831,8 +5765,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
           <t>future pause-detected variant</t>
@@ -5890,8 +5822,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
           <t>future pause-resumed variant</t>
@@ -5949,8 +5879,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
           <t>future shared cooldown variant</t>
@@ -6008,8 +5936,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
           <t>future shared cooldown variant</t>
@@ -6067,8 +5993,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
           <t>future shared recovery variant</t>
@@ -6126,8 +6050,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
           <t>future shared recovery variant</t>
@@ -6185,8 +6107,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
           <t>future shared warmup variant</t>
@@ -6244,8 +6164,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
           <t>future shared warmup variant</t>
@@ -6303,8 +6221,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
           <t>future HR correction variant</t>
@@ -6362,8 +6278,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
           <t>future HR correction variant</t>
@@ -6421,8 +6335,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
           <t>future HR correction variant</t>
@@ -6480,8 +6392,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
           <t>future HR correction variant</t>
@@ -6539,8 +6449,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
           <t>future HR correction variant</t>
@@ -6598,8 +6506,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
           <t>future HR correction variant</t>
@@ -6657,8 +6563,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
           <t>future HR correction variant</t>
@@ -6716,8 +6620,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
           <t>future HR correction variant</t>
@@ -6775,8 +6677,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
           <t>future HR hold variant</t>
@@ -6834,8 +6734,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
           <t>future HR hold variant</t>
@@ -6893,8 +6791,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
           <t>future HR hold variant</t>
@@ -6952,8 +6848,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
           <t>future HR hold variant</t>
@@ -7011,8 +6905,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
           <t>future easy-run motivation variant</t>
@@ -7070,8 +6962,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
           <t>future easy-run motivation variant</t>
@@ -7129,8 +7019,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
           <t>future easy-run motivation variant</t>
@@ -7188,8 +7076,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
           <t>future easy-run motivation variant</t>
@@ -7247,8 +7133,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
           <t>future interval motivation variant</t>
@@ -7306,8 +7190,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
           <t>future interval motivation variant</t>
@@ -7365,8 +7247,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
           <t>future interval motivation variant</t>
@@ -7424,8 +7304,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
           <t>future interval motivation variant</t>
@@ -7483,8 +7361,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
           <t>future countdown-start variant</t>
@@ -7542,8 +7418,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
           <t>future workout-finish variant</t>
@@ -7601,8 +7475,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
           <t>future workout-finish variant</t>
